--- a/workshop_registration_form_templates/035_hr_professional_certification_registration_form--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/035_hr_professional_certification_registration_form--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>certifying_body_other</t>
+          <t>certifying_body_other_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other Certifying Body</t>
+          <t>Certifying Body Other 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>certification_date</t>
+          <t>certification_date_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>certification_status</t>
+          <t>certification_status_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>certification_status_other</t>
+          <t>certification_status_other_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other Certification Status</t>
+          <t>Certification Status Other 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>certifying_body</t>
+          <t>certifying_body_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Certifying Body</t>
+          <t>Certifying Body 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>certifying_body_other</t>
+          <t>certifying_body_other_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other Certifying Body</t>
+          <t>Certifying Body Other 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>certifying_body_2</t>
+          <t>certifying_body_2_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Certifying Body 2</t>
+          <t>Certifying Body 2 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>certification_status_choices</t>
+          <t>certification_status_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>certification_status_choices</t>
+          <t>certification_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
